--- a/03_Outputs/all/01_TablasDescriptivas/idx10_juventud_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx10_juventud_vr.xlsx
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.646905314020701</v>
+        <v>1.646905314020698</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.127356175509725</v>
+        <v>1.127356175509724</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.047919478922423</v>
+        <v>1.047919478922419</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7878343789074421</v>
+        <v>0.7878343789074412</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.6255334874555057</v>
+        <v>0.6255334874555056</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5638463936739929</v>
+        <v>0.5638463936739917</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.3728390037000548</v>
+        <v>0.3728390037000546</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.1756815267807689</v>
+        <v>0.1756815267807681</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.07289258746472876</v>
+        <v>0.07289258746472874</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>6.855978627407099</v>
+        <v>6.855978627407096</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>7.983334802916825</v>
+        <v>7.98333480291682</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>9.031254281839248</v>
+        <v>9.031254281839241</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>9.81908866074669</v>
+        <v>9.819088660746681</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>10.4446221482022</v>
+        <v>10.44462214820219</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>11.00846854187619</v>
+        <v>11.00846854187618</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>11.38130754557624</v>
+        <v>11.38130754557623</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.7514258857545</v>
+        <v>11.75142588575449</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>11.92710741253527</v>
+        <v>11.92710741253526</v>
       </c>
       <c r="C24">
         <v>11</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>11.99999999999999</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>24.1065674555873</v>
+        <v>24.10656745558732</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>19.30237682263268</v>
+        <v>19.3023768226327</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>13.72421095017251</v>
+        <v>13.72421095017249</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>9.394634795914378</v>
+        <v>9.394634795914376</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>8.732662324353527</v>
+        <v>8.7326623243535</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>6.56528649089535</v>
+        <v>6.565286490895349</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>5.212779062129213</v>
+        <v>5.212779062129218</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>4.698719947283274</v>
+        <v>4.698719947283267</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>3.084319501485508</v>
+        <v>3.08431950148551</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.464012723173074</v>
+        <v>1.464012723173069</v>
       </c>
       <c r="C36">
         <v>11</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6074382288727396</v>
+        <v>0.6074382288727399</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>24.1065674555873</v>
+        <v>24.10656745558732</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>43.40894427821998</v>
+        <v>43.40894427822001</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>57.13315522839248</v>
+        <v>57.13315522839251</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>66.52779002430687</v>
+        <v>66.52779002430688</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>94.84422954646868</v>
+        <v>94.84422954646867</v>
       </c>
       <c r="C46">
         <v>9</v>

--- a/03_Outputs/all/01_TablasDescriptivas/idx10_juventud_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx10_juventud_vr.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.892788094670477</v>
+        <v>3.060912972092618</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>2.316285218715922</v>
+        <v>2.37867960418862</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.646905314020698</v>
+        <v>1.671744518459463</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.127356175509724</v>
+        <v>1.129692520919843</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.047919478922419</v>
+        <v>1.103011868538042</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7878343789074412</v>
+        <v>0.8227329452324187</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.6255334874555056</v>
+        <v>0.6922450162798036</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5638463936739917</v>
+        <v>0.5991203534952945</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.3728390037000546</v>
+        <v>0.5558148007604665</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.370118340178261</v>
+        <v>0.3727678563658327</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.1756815267807681</v>
+        <v>0.3671133688192086</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.07289258746472874</v>
+        <v>0.1740243361234451</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -595,14 +595,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>variance</t>
         </is>
       </c>
       <c r="B14">
-        <v>2.892788094670477</v>
+        <v>0.07213983872495171</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>5.209073313386398</v>
+        <v>3.060912972092618</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>6.855978627407096</v>
+        <v>5.439592576281237</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>7.98333480291682</v>
+        <v>7.1113370947407</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>9.031254281839241</v>
+        <v>8.241029615660542</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>9.819088660746681</v>
+        <v>9.344041484198584</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>10.44462214820219</v>
+        <v>10.166774429431</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>11.00846854187618</v>
+        <v>10.85901944571081</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>11.38130754557623</v>
+        <v>11.4581397992061</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.75142588575449</v>
+        <v>12.01395459996657</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>11.92710741253526</v>
+        <v>12.3867224563324</v>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>11.99999999999999</v>
+        <v>12.75383582515161</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -811,14 +811,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B26">
-        <v>24.10656745558732</v>
+        <v>12.92786016127505</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -829,14 +829,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B27">
-        <v>19.3023768226327</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>13.72421095017249</v>
+        <v>23.54548440071243</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>9.394634795914376</v>
+        <v>18.29753541683553</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>8.7326623243535</v>
+        <v>12.85957321891894</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>6.565286490895349</v>
+        <v>8.689942468614172</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>5.212779062129218</v>
+        <v>8.484706681061857</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>4.698719947283267</v>
+        <v>6.328714963326296</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>3.106991697500457</v>
+        <v>5.324961663690795</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>3.08431950148551</v>
+        <v>4.608618103809955</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.464012723173069</v>
+        <v>4.275498467388203</v>
       </c>
       <c r="C36">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6074382288727399</v>
+        <v>2.867445048967943</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1027,14 +1027,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B38">
-        <v>24.10656745558732</v>
+        <v>2.823948990916988</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1045,14 +1045,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B39">
-        <v>43.40894427822001</v>
+        <v>1.338648739411115</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1063,14 +1063,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B40">
-        <v>57.13315522839251</v>
+        <v>0.5549218363457821</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>66.52779002430688</v>
+        <v>23.54548440071243</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>75.26045234866039</v>
+        <v>41.84301981754796</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>81.82573883955574</v>
+        <v>54.70259303646691</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>87.03851790168495</v>
+        <v>63.39253550508107</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>91.73723784896822</v>
+        <v>71.87724218614292</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>94.84422954646867</v>
+        <v>78.20595714946921</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>97.92854904795418</v>
+        <v>83.53091881316001</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>99.39256177112726</v>
+        <v>88.13953691696997</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1229,12 +1229,84 @@
         </is>
       </c>
       <c r="B49">
+        <v>92.41503538435818</v>
+      </c>
+      <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>95.28248043332611</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>98.10642942424312</v>
+      </c>
+      <c r="C51">
+        <v>11</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>99.44507816365422</v>
+      </c>
+      <c r="C52">
+        <v>12</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B53">
         <v>100</v>
       </c>
-      <c r="C49">
-        <v>12</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C53">
+        <v>13</v>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>pca</t>
         </is>
